--- a/99. 부가업무/2. HVAC 보유 현황/HKMC_HVAC_보유_현황.xlsx
+++ b/99. 부가업무/2. HVAC 보유 현황/HKMC_HVAC_보유_현황.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\PROJECT\Gitlab\HMC\ptc_heater_doc\33. HVAC 관리\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\PROJECT\Gitlab\HMC\ptc_heater_doc\99. 부가업무\2. HVAC 보유 현황\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -130,18 +130,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>대당 약 130만원 요구</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>비고</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>O</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>24.10.15 수령</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -163,6 +155,14 @@
   </si>
   <si>
     <t>7월 말 경 입고 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/15 1EA, 7월 말 추가 1EA 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -540,7 +540,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
@@ -570,7 +570,7 @@
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -602,7 +602,7 @@
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -616,7 +616,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -630,7 +630,7 @@
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -641,12 +641,12 @@
       <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="E9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
@@ -662,7 +662,7 @@
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
@@ -690,7 +690,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/99. 부가업무/2. HVAC 보유 현황/HKMC_HVAC_보유_현황.xlsx
+++ b/99. 부가업무/2. HVAC 보유 현황/HKMC_HVAC_보유_현황.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <si>
     <t>자종</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -114,55 +114,72 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>진행중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24.10.15 수령</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아직 RHD 사양 미생산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베플 사양 보유중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8월 중순 경 -&gt; 말 입고 예정 변경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QV 동일사양</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8월 중~말 입고 예정
+-&gt; 변경 : 자동차측 물량 증대로, 9월말~10월쯤 입고 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>X</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>진행중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>진행중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>O</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>비고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>24.10.15 수령</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아직 RHD 사양 미생산</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>빠르면 8월 초 입고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8월 중~말 입고 예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8월 중순 경 입고 예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7월 말 경 입고 예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>진행중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7/15 1EA, 7월 말 추가 1EA 예정</t>
+    <t>진공주형 HVAC 입고 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/22 기준 약 2주 전 납품되어 조립 시작 예상으로, 두원 이벤트 대응 완료 후 수령 가능 예상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보유중</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -224,7 +241,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -236,6 +253,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -520,7 +540,7 @@
   <dimension ref="B2:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="7" max="7" width="52.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
@@ -540,7 +560,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
@@ -555,7 +575,9 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
@@ -566,7 +588,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
@@ -585,7 +607,9 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
@@ -595,14 +619,12 @@
         <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -616,21 +638,23 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="2" t="s">
-        <v>30</v>
+      <c r="G8" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -639,17 +663,15 @@
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>33</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
@@ -658,11 +680,11 @@
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="2" t="s">
-        <v>29</v>
+      <c r="G10" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
@@ -671,11 +693,13 @@
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
@@ -690,7 +714,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/99. 부가업무/2. HVAC 보유 현황/HKMC_HVAC_보유_현황.xlsx
+++ b/99. 부가업무/2. HVAC 보유 현황/HKMC_HVAC_보유_현황.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\PROJECT\Gitlab\HMC\ptc_heater_doc\99. 부가업무\2. HVAC 보유 현황\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KJG\3.Gitlab\HMC\ptc_heater_doc\99. 부가업무\2. HVAC 보유 현황\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>자종</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -147,10 +147,6 @@
   </si>
   <si>
     <t>O</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8월 중순 경 -&gt; 말 입고 예정 변경</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -180,6 +176,14 @@
   </si>
   <si>
     <t>보유중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9/3 입고완료</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -252,10 +256,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -564,7 +568,7 @@
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -580,19 +584,17 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="3"/>
+      <c r="B4" s="4"/>
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -608,11 +610,11 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -628,7 +630,7 @@
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="3"/>
+      <c r="B7" s="4"/>
       <c r="C7" s="2" t="s">
         <v>16</v>
       </c>
@@ -642,37 +644,37 @@
       </c>
     </row>
     <row r="8" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="4"/>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="4" t="s">
-        <v>33</v>
+      <c r="G8" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -683,12 +685,12 @@
         <v>23</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="4" t="s">
-        <v>37</v>
+      <c r="G10" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="3"/>
+      <c r="B11" s="4"/>
       <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
@@ -698,7 +700,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">

--- a/99. 부가업무/2. HVAC 보유 현황/HKMC_HVAC_보유_현황.xlsx
+++ b/99. 부가업무/2. HVAC 보유 현황/HKMC_HVAC_보유_현황.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KJG\3.Gitlab\HMC\ptc_heater_doc\99. 부가업무\2. HVAC 보유 현황\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\PROJECT\Gitlab\HMC\ptc_heater_doc\99. 부가업무\2. HVAC 보유 현황\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -134,10 +134,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아직 RHD 사양 미생산</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>베플 사양 보유중</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -154,11 +150,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>8월 중~말 입고 예정
--&gt; 변경 : 자동차측 물량 증대로, 9월말~10월쯤 입고 가능</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>X</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -171,10 +162,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>8/22 기준 약 2주 전 납품되어 조립 시작 예상으로, 두원 이벤트 대응 완료 후 수령 가능 예상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>보유중</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -184,6 +171,18 @@
   </si>
   <si>
     <t>9/3 입고완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시작시험팀 보유, 사용 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아직 한온 설계팀도 못 받음, 9/22 한온 가서 요청한다고 함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-&gt; 변경 : 자동차측 물량 증대로, 9월말~10월쯤 입고 가능</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -245,7 +244,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -260,6 +259,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -580,7 +582,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -589,12 +591,12 @@
         <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -610,7 +612,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -621,12 +623,12 @@
         <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -640,23 +642,23 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="3" t="s">
-        <v>32</v>
+      <c r="G8" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -665,15 +667,15 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -686,7 +688,7 @@
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
@@ -700,7 +702,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
